--- a/sources/hose2.xlsx
+++ b/sources/hose2.xlsx
@@ -558,7 +558,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>NORTHERN STAR RESOURCES LIMITED</t>
+          <t>OWNER</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KCGM GROWTH PROJECT</t>
+          <t>GROWTH PROJECT</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>23517</t>
+          <t/>
         </is>
       </c>
     </row>
